--- a/results/tables/04_community_composition_measures/table3_pollution_pc_species_pc_regression.xlsx
+++ b/results/tables/04_community_composition_measures/table3_pollution_pc_species_pc_regression.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.6</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0999</v>
+        <v>0.0003</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0843</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3">
@@ -507,16 +507,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0218</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0192</v>
+        <v>-0.7247</v>
       </c>
       <c r="G3" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.5</v>
+        <v>13.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001</v>
+        <v>0.0261</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0057</v>
+        <v>0.715</v>
       </c>
       <c r="G4" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0396</v>
+        <v>0.1916</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0312</v>
+        <v>-1.5203</v>
       </c>
       <c r="G5" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0113</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0076</v>
+        <v>0.0107</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0119</v>
+        <v>0.2982</v>
       </c>
       <c r="G7" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8">
@@ -633,25 +633,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6.1</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>0.024</v>
+        <v>0.0127</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0211</v>
+        <v>-1.5544</v>
       </c>
       <c r="G8" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9">
@@ -665,20 +665,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23.6</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0139</v>
+        <v>0.138</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0288</v>
+        <v>4.8349</v>
       </c>
       <c r="G9" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
@@ -692,20 +692,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0818</v>
+        <v>0.0328</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.053</v>
+        <v>2.1217</v>
       </c>
       <c r="G10" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -719,20 +719,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0195</v>
+        <v>0.0014</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0227</v>
+        <v>0.3441</v>
       </c>
       <c r="G11" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -746,20 +746,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0271</v>
+        <v>0.0005</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0236</v>
+        <v>0.175</v>
       </c>
       <c r="G12" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -773,20 +773,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0028</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0071</v>
+        <v>-0.0408</v>
       </c>
       <c r="G13" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -795,25 +795,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0075</v>
+        <v>0.0056</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0108</v>
+        <v>-0.7486</v>
       </c>
       <c r="G14" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15">
@@ -822,25 +822,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6.1</v>
+        <v>17.8</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0375</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.024</v>
+        <v>-0.8682</v>
       </c>
       <c r="G15" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16">
@@ -854,20 +854,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>23.6</v>
+        <v>13.8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0407</v>
+        <v>0.0018</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0488</v>
+        <v>0.3625</v>
       </c>
       <c r="G16" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
@@ -881,20 +881,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0038</v>
+        <v>0.0036</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0114</v>
+        <v>0.3989</v>
       </c>
       <c r="G17" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18">
@@ -908,20 +908,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.5</v>
+        <v>6.7</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0774</v>
+        <v>0.0097</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.045</v>
+        <v>-0.5726</v>
       </c>
       <c r="G18" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19">
@@ -935,20 +935,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8.199999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0438</v>
+        <v>0.0017</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0298</v>
+        <v>-0.228</v>
       </c>
       <c r="G19" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20">
@@ -957,25 +957,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0023</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0125</v>
+        <v>0.5927</v>
       </c>
       <c r="G20" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21">
@@ -984,25 +984,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6.2</v>
+        <v>17.8</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0017</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0051</v>
+        <v>-3.0089</v>
       </c>
       <c r="G21" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22">
@@ -1011,25 +1011,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6.1</v>
+        <v>13.8</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0026</v>
+        <v>0.0128</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0063</v>
+        <v>1.1991</v>
       </c>
       <c r="G22" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23">
@@ -1043,20 +1043,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0029</v>
+        <v>0.0098</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0138</v>
+        <v>-0.8228</v>
       </c>
       <c r="G23" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24">
@@ -1070,20 +1070,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.6</v>
+        <v>6.7</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0017</v>
+        <v>0.0076</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.008</v>
+        <v>0.6278</v>
       </c>
       <c r="G24" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25">
@@ -1097,20 +1097,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.5</v>
+        <v>6.1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0004</v>
+        <v>0.0205</v>
       </c>
       <c r="G25" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0057</v>
+        <v>0.0205</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0114</v>
+        <v>-7.124</v>
       </c>
       <c r="G26" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27">
@@ -1146,25 +1146,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>17.8</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0078</v>
+        <v>0.0108</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0124</v>
+        <v>4.8763</v>
       </c>
       <c r="G27" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28">
@@ -1173,25 +1173,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6.2</v>
+        <v>13.8</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0012</v>
+        <v>0.0075</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0045</v>
+        <v>-3.6771</v>
       </c>
       <c r="G28" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29">
@@ -1200,25 +1200,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0026</v>
+        <v>0.0001</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0067</v>
+        <v>0.2795</v>
       </c>
       <c r="G29" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30">
@@ -1232,20 +1232,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>23.6</v>
+        <v>6.7</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0034</v>
+        <v>0.0066</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.014</v>
+        <v>-2.3393</v>
       </c>
       <c r="G30" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31">
@@ -1259,20 +1259,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.6</v>
+        <v>6.1</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0518</v>
+        <v>0.0037</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0417</v>
+        <v>-1.67</v>
       </c>
       <c r="G31" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32">
@@ -1281,25 +1281,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0072</v>
+        <v>0.0145</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0136</v>
+        <v>-2.6841</v>
       </c>
       <c r="G32" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33">
@@ -1308,25 +1308,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8.199999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="E33" t="n">
-        <v>0.016</v>
+        <v>0.0119</v>
       </c>
       <c r="F33" t="n">
-        <v>0.018</v>
+        <v>-2.2993</v>
       </c>
       <c r="G33" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34">
@@ -1335,25 +1335,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>13.8</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0056</v>
+        <v>0.0051</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0098</v>
+        <v>-1.3516</v>
       </c>
       <c r="G34" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35">
@@ -1362,25 +1362,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0007</v>
+        <v>0.0086</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.0033</v>
+        <v>1.379</v>
       </c>
       <c r="G35" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36">
@@ -1389,25 +1389,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>PC6</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>PC5</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>PC7</t>
-        </is>
-      </c>
       <c r="D36" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0036</v>
+        <v>0.0017</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.0074</v>
+        <v>-0.5392</v>
       </c>
       <c r="G36" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37">
@@ -1421,182 +1421,182 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>23.6</v>
+        <v>6.1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.008</v>
+        <v>0.0206</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0224</v>
+        <v>-1.7751</v>
       </c>
       <c r="G37" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.6</v>
+        <v>41.6</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0034</v>
+        <v>0.0165</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.0112</v>
+        <v>1.5821</v>
       </c>
       <c r="G38" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.5</v>
+        <v>15.4</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0722</v>
+        <v>0.0905</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.045</v>
+        <v>-1.9</v>
       </c>
       <c r="G39" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8.199999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0002</v>
+        <v>0.265</v>
       </c>
       <c r="F40" t="n">
-        <v>0.002</v>
+        <v>-2.234</v>
       </c>
       <c r="G40" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0045</v>
+        <v>0.0365</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.0091</v>
+        <v>0.9869</v>
       </c>
       <c r="G41" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6.2</v>
+        <v>41.6</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0414</v>
+        <v>0.1264</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0262</v>
+        <v>-6.1542</v>
       </c>
       <c r="G42" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6.1</v>
+        <v>15.4</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0166</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.0164</v>
+        <v>-2.6987</v>
       </c>
       <c r="G43" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44">
@@ -1605,25 +1605,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>23.7</v>
+        <v>11.7</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0484</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.0607</v>
+        <v>0.0018</v>
       </c>
       <c r="G44" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
@@ -1632,25 +1632,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>17.8</v>
+        <v>6.8</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>0.0141</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.0007</v>
+        <v>0.8619</v>
       </c>
       <c r="G45" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46">
@@ -1659,25 +1659,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>15.4</v>
+        <v>41.6</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0332</v>
+        <v>0.015</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0406</v>
+        <v>2.1617</v>
       </c>
       <c r="G46" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47">
@@ -1686,25 +1686,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.3</v>
+        <v>15.4</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0002</v>
+        <v>0.0809</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0026</v>
+        <v>2.5804</v>
       </c>
       <c r="G47" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48">
@@ -1713,25 +1713,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7.7</v>
+        <v>11.7</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1592</v>
+        <v>0.0549</v>
       </c>
       <c r="F48" t="n">
-        <v>0.063</v>
+        <v>1.461</v>
       </c>
       <c r="G48" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49">
@@ -1740,25 +1740,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>23.7</v>
+        <v>6.8</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0849</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1146</v>
+        <v>0.0178</v>
       </c>
       <c r="G49" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50">
@@ -1767,25 +1767,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>17.8</v>
+        <v>41.6</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0077</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.03</v>
+        <v>1.895</v>
       </c>
       <c r="G50" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51">
@@ -1794,25 +1794,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>15.4</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1271</v>
+        <v>0.0118</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1132</v>
+        <v>1.1487</v>
       </c>
       <c r="G51" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52">
@@ -1821,25 +1821,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.3</v>
+        <v>11.7</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0631</v>
+        <v>0.0466</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0711</v>
+        <v>1.5657</v>
       </c>
       <c r="G52" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53">
@@ -1848,25 +1848,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0526</v>
+        <v>0.0056</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0516</v>
+        <v>-0.6466</v>
       </c>
       <c r="G53" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1884,16 +1884,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>23.7</v>
+        <v>41.6</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0593</v>
+        <v>0.0056</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1086</v>
+        <v>-3.1908</v>
       </c>
       <c r="G54" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1911,16 +1911,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>17.8</v>
+        <v>15.4</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0004</v>
+        <v>0.0046</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0078</v>
+        <v>1.493</v>
       </c>
       <c r="G55" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1938,16 +1938,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15.4</v>
+        <v>11.7</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0043</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0235</v>
+        <v>1.4568</v>
       </c>
       <c r="G56" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.3</v>
+        <v>6.8</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0211</v>
+        <v>0.0201</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.0466</v>
+        <v>-2.5504</v>
       </c>
       <c r="G57" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58">
@@ -1983,25 +1983,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>7.7</v>
+        <v>41.6</v>
       </c>
       <c r="E58" t="n">
-        <v>0.251</v>
+        <v>0.0023</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1279</v>
+        <v>1.361</v>
       </c>
       <c r="G58" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59">
@@ -2010,25 +2010,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>23.7</v>
+        <v>15.4</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0608</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.0607</v>
+        <v>-0.0152</v>
       </c>
       <c r="G59" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60">
@@ -2037,25 +2037,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>17.8</v>
+        <v>11.7</v>
       </c>
       <c r="E60" t="n">
-        <v>0.08</v>
+        <v>0.0155</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0603</v>
+        <v>-1.2392</v>
       </c>
       <c r="G60" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61">
@@ -2064,349 +2064,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>15.4</v>
+        <v>6.8</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3287</v>
+        <v>0.027</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.1139</v>
+        <v>-1.9459</v>
       </c>
       <c r="G61" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>1</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>PC4</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>PC4</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.06610000000000001</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-0.0455</v>
-      </c>
-      <c r="G62" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>1</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>PC4</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>PC5</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-0.0003</v>
-      </c>
-      <c r="G63" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>1</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>PC5</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>PC1</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.1568</v>
-      </c>
-      <c r="F64" t="n">
-        <v>-0.1837</v>
-      </c>
-      <c r="G64" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>1</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>PC5</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>PC2</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-0.0203</v>
-      </c>
-      <c r="G65" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>1</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>PC5</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0.0402</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.0751</v>
-      </c>
-      <c r="G66" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>1</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>PC5</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>PC4</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0.0238</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="G67" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>1</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>PC5</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>PC5</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0.0482</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-0.0583</v>
-      </c>
-      <c r="G68" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>1</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>PC6</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>PC1</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0.0157</v>
-      </c>
-      <c r="G69" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>1</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>PC6</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>PC2</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="G70" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>1</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>PC6</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0.0391</v>
-      </c>
-      <c r="F71" t="n">
-        <v>-0.0471</v>
-      </c>
-      <c r="G71" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>1</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>PC6</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>PC4</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="F72" t="n">
-        <v>-0.0022</v>
-      </c>
-      <c r="G72" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>1</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>PC6</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>PC5</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0.009599999999999999</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0.0165</v>
-      </c>
-      <c r="G73" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
